--- a/output/pdf_financials_xlsx/RML.xlsx
+++ b/output/pdf_financials_xlsx/RML.xlsx
@@ -1320,10 +1320,10 @@
         <v>-18.686</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>25.49</v>
+        <v>-25.49</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>35.272</v>
+        <v>-35.272</v>
       </c>
       <c r="Q16" s="1" t="inlineStr">
         <is>
@@ -1612,10 +1612,10 @@
         <v>-18.686</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>25.49</v>
+        <v>-25.49</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>35.272</v>
+        <v>-35.272</v>
       </c>
       <c r="Q20" s="1" t="inlineStr">
         <is>
@@ -1787,10 +1787,10 @@
         <v>-18.686</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>25.49</v>
+        <v>-25.49</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>35.272</v>
+        <v>-35.272</v>
       </c>
       <c r="Q23" s="1" t="inlineStr">
         <is>
@@ -1964,10 +1964,10 @@
         <v>622.866667</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>637.25</v>
+        <v>-637.25</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>503.885714</v>
+        <v>-503.885714</v>
       </c>
       <c r="Q26" s="1" t="inlineStr">
         <is>
@@ -2023,10 +2023,10 @@
         <v>-18.686</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>25.49</v>
+        <v>-25.49</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>35.272</v>
+        <v>-35.272</v>
       </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
@@ -2141,10 +2141,10 @@
         <v>-18.686</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>25.49</v>
+        <v>-25.49</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>35.272</v>
+        <v>-35.272</v>
       </c>
       <c r="Q29" s="1" t="inlineStr">
         <is>
@@ -2283,10 +2283,10 @@
         <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="1" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>-13.939</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>73.719821</v>
+        <v>-73.719821</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>-8.101003</v>
@@ -30222,7 +30222,7 @@
         </is>
       </c>
       <c r="K230" s="5" t="n">
-        <v>73.719821</v>
+        <v>-73.719821</v>
       </c>
       <c r="L230" s="5" t="n">
         <v>-8.101003</v>
@@ -39656,7 +39656,7 @@
         </is>
       </c>
       <c r="S328" s="5" t="n">
-        <v>35.272</v>
+        <v>-35.272</v>
       </c>
       <c r="T328" t="inlineStr">
         <is>
@@ -42059,10 +42059,10 @@
         </is>
       </c>
       <c r="R353" s="5" t="n">
-        <v>25.49</v>
+        <v>-25.49</v>
       </c>
       <c r="S353" s="5" t="n">
-        <v>40.711</v>
+        <v>-40.711</v>
       </c>
       <c r="T353" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/RML.xlsx
+++ b/output/pdf_financials_xlsx/RML.xlsx
@@ -1084,10 +1084,10 @@
         <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.102</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.123</v>
       </c>
       <c r="Q12" s="1" t="inlineStr">
         <is>
@@ -2023,10 +2023,10 @@
         <v>-18.686</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-25.49</v>
+        <v>-25.388</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-35.272</v>
+        <v>-35.149</v>
       </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
@@ -2141,10 +2141,10 @@
         <v>-18.686</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-25.49</v>
+        <v>-25.388</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-35.272</v>
+        <v>-35.149</v>
       </c>
       <c r="Q29" s="1" t="inlineStr">
         <is>
@@ -2391,49 +2391,49 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.245</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>10.42</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>3.382</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.903</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.192</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.036153</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.968843</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.289542</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.05144</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.000228</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.000136</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>3.6e-05</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.857</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.857</v>
       </c>
       <c r="Q34" s="1" t="inlineStr">
         <is>
@@ -2505,49 +2505,49 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.245</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>3.806</v>
+        <v>14.226</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>3.382</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.903</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.192</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.036153</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.968843</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.289542</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.05144</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.000228</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.000136</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>3.6e-05</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>1.857</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>1.857</v>
       </c>
       <c r="Q36" s="1" t="inlineStr">
         <is>
@@ -3189,34 +3189,34 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>14.079</v>
+        <v>11.834</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>18.508</v>
+        <v>8.087999999999999</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>15.082</v>
+        <v>11.7</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.389</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.903</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.192</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.036153</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.97228</v>
+        <v>0.003437</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.301349</v>
+        <v>0.011807</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.053499</v>
+        <v>0.002059</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0</v>
@@ -8720,7 +8720,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12590,7 +12590,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -17200,7 +17200,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -19726,7 +19726,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
@@ -39092,7 +39092,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -41424,7 +41424,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">

--- a/output/pdf_financials_xlsx/RML.xlsx
+++ b/output/pdf_financials_xlsx/RML.xlsx
@@ -594,10 +594,8 @@
       <c r="K4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>0</v>
@@ -653,10 +651,8 @@
       <c r="K5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>0</v>
@@ -718,10 +714,8 @@
       <c r="K6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>0</v>
@@ -777,10 +771,8 @@
       <c r="K7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>0</v>
@@ -836,10 +828,8 @@
       <c r="K8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>0</v>
@@ -895,10 +885,8 @@
       <c r="K9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>0</v>
@@ -954,10 +942,8 @@
       <c r="K10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>0</v>
@@ -1013,10 +999,8 @@
       <c r="K11" s="3" t="n">
         <v>-3.79497</v>
       </c>
-      <c r="L11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L11" s="3" t="n">
+        <v>-1.740352</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>-1.096887</v>
@@ -1072,10 +1056,8 @@
       <c r="K12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -1131,10 +1113,8 @@
       <c r="K13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="L13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>-0</v>
@@ -1190,10 +1170,8 @@
       <c r="K14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>0</v>
@@ -1249,10 +1227,8 @@
       <c r="K15" s="3" t="n">
         <v>-0.559419</v>
       </c>
-      <c r="L15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L15" s="3" t="n">
+        <v>0.387666</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>-0.02995</v>
@@ -1308,10 +1284,8 @@
       <c r="K16" s="3" t="n">
         <v>-11.600198</v>
       </c>
-      <c r="L16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L16" s="3" t="n">
+        <v>-15.274434</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>-14.186659</v>
@@ -1367,10 +1341,8 @@
       <c r="K17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="L17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>-0</v>
@@ -1600,10 +1572,8 @@
       <c r="K20" s="3" t="n">
         <v>-11.600198</v>
       </c>
-      <c r="L20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L20" s="3" t="n">
+        <v>-15.274434</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-14.186659</v>
@@ -1659,10 +1629,8 @@
       <c r="K21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>0</v>
@@ -1718,10 +1686,8 @@
       <c r="K22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>0</v>
@@ -1834,10 +1800,8 @@
       <c r="K24" s="3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="L24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L24" s="3" t="n">
+        <v>-0.03</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>-0.03</v>
@@ -1893,10 +1857,8 @@
       <c r="K25" s="3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="L25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L25" s="3" t="n">
+        <v>-0.03</v>
       </c>
       <c r="M25" s="3" t="n">
         <v>-0.03</v>
@@ -1952,10 +1914,8 @@
       <c r="K26" s="3" t="n">
         <v>580.0099</v>
       </c>
-      <c r="L26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L26" s="3" t="n">
+        <v>509.1478</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>472.888633</v>
@@ -2011,10 +1971,8 @@
       <c r="K27" s="3" t="n">
         <v>-11.600198</v>
       </c>
-      <c r="L27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L27" s="3" t="n">
+        <v>-15.274434</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-14.186659</v>
@@ -2070,10 +2028,8 @@
       <c r="K28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>0</v>
@@ -2129,10 +2085,8 @@
       <c r="K29" s="3" t="n">
         <v>-11.600198</v>
       </c>
-      <c r="L29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L29" s="3" t="n">
+        <v>-15.274434</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-14.186659</v>
@@ -2271,10 +2225,8 @@
       <c r="K31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="L31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>-0</v>
@@ -4179,54 +4131,52 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>13.722</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>7.557</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>34.111</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>30.151</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>48.459</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>47.879</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>8.287986</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>8.294684</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>7.110007</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>9.461802</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>9.366374</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>9.747247</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>9.868</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>11.311</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>13.646</v>
+      </c>
+      <c r="Q64" s="3" t="n">
+        <v>22.876</v>
       </c>
     </row>
     <row r="65">
@@ -4350,19 +4300,19 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>16.866</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>19.571</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>29.103</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>38.579</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>23.378</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>0</v>
@@ -6664,10 +6614,10 @@
         <v>6.843</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>0.827</v>
       </c>
       <c r="F107" s="3" t="n">
         <v>0.15</v>
@@ -7114,7 +7064,7 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -8407,7 +8357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T490"/>
+  <dimension ref="A1:T499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -23060,7 +23010,11 @@
           <t>GST recoverable 6</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -31990,7 +31944,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -33988,7 +33946,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -35714,7 +35676,11 @@
           <t>Recovery of future income taxes</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E288" s="5" t="n">
         <v>-13.189</v>
       </c>
@@ -36958,7 +36924,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E301" s="5" t="n">
         <v>0.6909999999999999</v>
       </c>
@@ -43055,10 +43025,8 @@
       <c r="N364" s="5" t="n">
         <v>3.597765</v>
       </c>
-      <c r="O364" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O364" s="5" t="n">
+        <v>0.670909</v>
       </c>
       <c r="P364" s="5" t="n">
         <v>1.126837</v>
@@ -43323,10 +43291,8 @@
       <c r="N367" s="5" t="n">
         <v>-3.79497</v>
       </c>
-      <c r="O367" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O367" s="5" t="n">
+        <v>-1.740352</v>
       </c>
       <c r="P367" s="5" t="n">
         <v>-1.096887</v>
@@ -43409,10 +43375,8 @@
       <c r="N368" s="5" t="n">
         <v>7.121041</v>
       </c>
-      <c r="O368" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O368" s="5" t="n">
+        <v>7.937264</v>
       </c>
       <c r="P368" s="5" t="n">
         <v>9.861102000000001</v>
@@ -43495,10 +43459,8 @@
       <c r="N369" s="5" t="n">
         <v>1.76486</v>
       </c>
-      <c r="O369" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O369" s="5" t="n">
+        <v>2.167234</v>
       </c>
       <c r="P369" s="5" t="n">
         <v>3.301017</v>
@@ -43773,10 +43735,8 @@
       <c r="N372" s="5" t="n">
         <v>7.805228</v>
       </c>
-      <c r="O372" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O372" s="5" t="n">
+        <v>13.534082</v>
       </c>
       <c r="P372" s="5" t="n">
         <v>13.089772</v>
@@ -43960,15 +43920,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N374" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O374" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N374" s="5" t="n">
+        <v>-11.600198</v>
+      </c>
+      <c r="O374" s="5" t="n">
+        <v>-15.274434</v>
       </c>
       <c r="P374" s="5" t="n">
         <v>-14.186659</v>
@@ -44057,10 +44013,8 @@
       <c r="N375" s="5" t="n">
         <v>-2e-08</v>
       </c>
-      <c r="O375" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O375" s="5" t="n">
+        <v>-3e-08</v>
       </c>
       <c r="P375" s="5" t="n">
         <v>-3e-08</v>
@@ -44146,15 +44100,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N376" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O376" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N376" s="5" t="n">
+        <v>544.777876</v>
+      </c>
+      <c r="O376" s="5" t="n">
+        <v>544.810623</v>
       </c>
       <c r="P376" s="5" t="n">
         <v>544.810623</v>
@@ -44191,10 +44141,14 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Stock based compensation (Note 9)</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr"/>
+          <t>Foreign exchange loss (gain)</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -44230,19 +44184,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L377" s="5" t="n">
-        <v>0.012124</v>
-      </c>
-      <c r="M377" s="5" t="n">
-        <v>1.480006</v>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N377" s="5" t="n">
-        <v>0.756624</v>
-      </c>
-      <c r="O377" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.559419</v>
+      </c>
+      <c r="O377" s="5" t="n">
+        <v>0.387666</v>
       </c>
       <c r="P377" t="inlineStr">
         <is>
@@ -44283,7 +44239,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Loss (gain) on revaluation of gold sale contract (Note 5)</t>
+          <t>Share based compensation (Note 9)</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
@@ -44317,22 +44273,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K378" s="5" t="n">
-        <v>-0.80966</v>
-      </c>
-      <c r="L378" s="5" t="n">
-        <v>0.603757</v>
-      </c>
-      <c r="M378" s="5" t="n">
-        <v>1.743214</v>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N378" s="5" t="n">
-        <v>-0.252955</v>
-      </c>
-      <c r="O378" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.756624</v>
+      </c>
+      <c r="O378" s="5" t="n">
+        <v>0.681777</v>
       </c>
       <c r="P378" t="inlineStr">
         <is>
@@ -44368,12 +44328,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Decommissioning and restoration provision and currency</t>
+          <t>OPERATING EXPENSES</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Decommissioning and restoration provision and currency devaluation (Note 2(b) and 6)</t>
+          <t>Loss (gain) on revaluation of gold sale contract (Note 5)</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
@@ -44407,26 +44367,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L379" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K379" s="5" t="n">
+        <v>-0.80966</v>
+      </c>
+      <c r="L379" s="5" t="n">
+        <v>0.603757</v>
       </c>
       <c r="M379" s="5" t="n">
-        <v>-0.609833</v>
+        <v>1.743214</v>
       </c>
       <c r="N379" s="5" t="n">
-        <v>-0.827718</v>
-      </c>
-      <c r="O379" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.252955</v>
+      </c>
+      <c r="O379" s="5" t="n">
+        <v>3.419076</v>
       </c>
       <c r="P379" t="inlineStr">
         <is>
@@ -44467,7 +44421,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Gain on transfer of convertible loan (Note 7)</t>
+          <t>Decommissioning and restoration provision and currency devaluation (Note 2(b) and 6)</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
@@ -44512,17 +44466,13 @@
         </is>
       </c>
       <c r="M380" s="5" t="n">
-        <v>-1.331691</v>
-      </c>
-      <c r="N380" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O380" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.609833</v>
+      </c>
+      <c r="N380" s="5" t="n">
+        <v>-0.827718</v>
+      </c>
+      <c r="O380" s="5" t="n">
+        <v>0.010508</v>
       </c>
       <c r="P380" t="inlineStr">
         <is>
@@ -44558,7 +44508,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Decommissioning and restoration provision and currency</t>
+          <t>NET LOSS AND COMPREHENSIVE LOSS</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -44611,16 +44561,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M381" s="5" t="n">
-        <v>-10.830342</v>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N381" s="5" t="n">
         <v>-11.600198</v>
       </c>
-      <c r="O381" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O381" s="5" t="n">
+        <v>-15.274434</v>
       </c>
       <c r="P381" t="inlineStr">
         <is>
@@ -44656,12 +44606,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Attributable to</t>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Attributable to total</t>
+          <t>Shareholders' deficiency (93,164,255) 756,624 1,466 (11,600,198) (104,006,363) 681,777</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -44675,34 +44625,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G382" s="5" t="n">
-        <v>-780.1369999999999</v>
-      </c>
-      <c r="H382" s="5" t="n">
-        <v>-44.313</v>
-      </c>
-      <c r="I382" s="5" t="n">
-        <v>25.881</v>
-      </c>
-      <c r="J382" s="5" t="n">
-        <v>-13.939</v>
-      </c>
-      <c r="K382" s="5" t="n">
-        <v>73.719821</v>
-      </c>
-      <c r="L382" s="5" t="n">
-        <v>-8.101003</v>
-      </c>
-      <c r="M382" s="5" t="n">
-        <v>-10.830342</v>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N382" s="5" t="n">
-        <v>-11.600198</v>
-      </c>
-      <c r="O382" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-118.59902</v>
+      </c>
+      <c r="O382" s="5" t="n">
+        <v>-15.274434</v>
       </c>
       <c r="P382" t="inlineStr">
         <is>
@@ -44738,12 +44700,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>WEIGHTED AVERAGE NUMBER OF SHARES</t>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>OUTSTANDING - Basic and diluted</t>
+          <t>Non- controlling interests (19,669,467) - - - (19,669,467) -</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -44777,17 +44739,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K383" s="5" t="n">
-        <v>532.621</v>
-      </c>
-      <c r="L383" s="5" t="n">
-        <v>533.159938</v>
-      </c>
-      <c r="M383" s="5" t="n">
-        <v>544.727491</v>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N383" s="5" t="n">
-        <v>544.777876</v>
+        <v>-19.669467</v>
       </c>
       <c r="O383" t="inlineStr">
         <is>
@@ -44828,12 +44796,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>WEIGHTED AVERAGE NUMBER OF SHARES</t>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>WEIGHTED AVERAGE NUMBER OF SHARES total</t>
+          <t>Deficit (877,518,673) - - (11,600,198) (889,118,871) -</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -44877,16 +44845,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M384" s="5" t="n">
-        <v>-104.006363</v>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N384" s="5" t="n">
-        <v>-11.600198</v>
-      </c>
-      <c r="O384" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-904.3933050000001</v>
+      </c>
+      <c r="O384" s="5" t="n">
+        <v>-15.274434</v>
       </c>
       <c r="P384" t="inlineStr">
         <is>
@@ -44922,15 +44890,19 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>$                 $                                                                                                    Shareholders'  Deficiency                    (84,369,289)$    555,370</t>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>- -      (10,830,342)     (877,518,673) - -      (11,600,198)     (889,118,871)                                                              Deficit                      (866,688,331)</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr"/>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING total</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr">
         <is>
           <t>-</t>
@@ -45020,12 +44992,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>$                 $                                                                                                    Shareholders'  Deficiency                    (84,369,289)$    555,370</t>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>surplus 756,624 66,753,692</t>
+          <t>surplus 756,624 681,777 Contributed 65,997,068</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -45069,16 +45041,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M386" s="5" t="n">
-        <v>65.997068</v>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N386" s="5" t="n">
-        <v>1.480006</v>
-      </c>
-      <c r="O386" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>67.435469</v>
+      </c>
+      <c r="O386" s="5" t="n">
+        <v>66.753692</v>
       </c>
       <c r="P386" t="inlineStr">
         <is>
@@ -45114,12 +45086,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>OPERATING EXPENSES</t>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Loss on revaluation of gold sale contract (Note 5)</t>
+          <t>- 1,466 - - - Amount 738,026,817</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -45158,21 +45130,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L387" s="5" t="n">
-        <v>0.603757</v>
-      </c>
-      <c r="M387" s="5" t="n">
-        <v>1.743214</v>
-      </c>
-      <c r="N387" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O387" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N387" s="5" t="n">
+        <v>738.028283</v>
+      </c>
+      <c r="O387" s="5" t="n">
+        <v>738.028283</v>
       </c>
       <c r="P387" t="inlineStr">
         <is>
@@ -45213,7 +45185,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Increase in decommissioning and restoration provision (Note 6)</t>
+          <t>Stock based compensation (Note 9)</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -45253,15 +45225,13 @@
         </is>
       </c>
       <c r="L388" s="5" t="n">
-        <v>1.915058</v>
+        <v>0.012124</v>
       </c>
       <c r="M388" s="5" t="n">
-        <v>2.812516</v>
-      </c>
-      <c r="N388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.480006</v>
+      </c>
+      <c r="N388" s="5" t="n">
+        <v>0.756624</v>
       </c>
       <c r="O388" t="inlineStr">
         <is>
@@ -45302,19 +45272,15 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>OPERATING EXPENSES</t>
+          <t>Decommissioning and restoration provision and currency</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Other income</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Gain on transfer of convertible loan (Note 7)</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr">
         <is>
           <t>-</t>
@@ -45350,13 +45316,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L389" s="5" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="M389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M389" s="5" t="n">
+        <v>-1.331691</v>
       </c>
       <c r="N389" t="inlineStr">
         <is>
@@ -45402,15 +45368,19 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>OPERATING EXPENSES</t>
+          <t>Decommissioning and restoration provision and currency</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Gain on transfer of convertible loan (Note 7)</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr"/>
+          <t>NET LOSS AND COMPREHENSIVE LOSS</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr">
         <is>
           <t>-</t>
@@ -45452,12 +45422,10 @@
         </is>
       </c>
       <c r="M390" s="5" t="n">
-        <v>-1.331691</v>
-      </c>
-      <c r="N390" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-10.830342</v>
+      </c>
+      <c r="N390" s="5" t="n">
+        <v>-11.600198</v>
       </c>
       <c r="O390" t="inlineStr">
         <is>
@@ -45498,12 +45466,12 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>OPERATING EXPENSES</t>
+          <t>Attributable to</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Foreign exchange gain on currency devaluation (Note 2(b))</t>
+          <t>Attributable to total</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
@@ -45517,37 +45485,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G391" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H391" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G391" s="5" t="n">
+        <v>-780.1369999999999</v>
+      </c>
+      <c r="H391" s="5" t="n">
+        <v>-44.313</v>
       </c>
       <c r="I391" s="5" t="n">
-        <v>-33.078</v>
-      </c>
-      <c r="J391" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>25.881</v>
+      </c>
+      <c r="J391" s="5" t="n">
+        <v>-13.939</v>
       </c>
       <c r="K391" s="5" t="n">
-        <v>-93.822</v>
+        <v>73.719821</v>
       </c>
       <c r="L391" s="5" t="n">
-        <v>-3.520758</v>
+        <v>-8.101003</v>
       </c>
       <c r="M391" s="5" t="n">
-        <v>-3.422349</v>
-      </c>
-      <c r="N391" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-10.830342</v>
+      </c>
+      <c r="N391" s="5" t="n">
+        <v>-11.600198</v>
       </c>
       <c r="O391" t="inlineStr">
         <is>
@@ -45588,19 +45548,15 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>OPERATING EXPENSES</t>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>OPERATING EXPENSES total</t>
-        </is>
-      </c>
-      <c r="D392" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>OUTSTANDING - Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr"/>
       <c r="E392" t="inlineStr">
         <is>
           <t>-</t>
@@ -45621,25 +45577,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I392" s="5" t="n">
-        <v>2.055</v>
-      </c>
-      <c r="J392" s="5" t="n">
-        <v>1.243</v>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K392" s="5" t="n">
-        <v>0.617</v>
+        <v>532.621</v>
       </c>
       <c r="L392" s="5" t="n">
-        <v>6.354242</v>
+        <v>533.159938</v>
       </c>
       <c r="M392" s="5" t="n">
-        <v>7.762497</v>
-      </c>
-      <c r="N392" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>544.727491</v>
+      </c>
+      <c r="N392" s="5" t="n">
+        <v>544.777876</v>
       </c>
       <c r="O392" t="inlineStr">
         <is>
@@ -45680,19 +45638,15 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>OPERATING EXPENSES</t>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>NET LOSS AND COMPREHENSIVE LOSS</t>
-        </is>
-      </c>
-      <c r="D393" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES total</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr"/>
       <c r="E393" t="inlineStr">
         <is>
           <t>-</t>
@@ -45728,16 +45682,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L393" s="5" t="n">
-        <v>-8.101003</v>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M393" s="5" t="n">
-        <v>-10.830342</v>
-      </c>
-      <c r="N393" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-104.006363</v>
+      </c>
+      <c r="N393" s="5" t="n">
+        <v>-11.600198</v>
       </c>
       <c r="O393" t="inlineStr">
         <is>
@@ -45778,12 +45732,12 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>WEIGHTED AVERAGE NUMBER OF SHARES</t>
+          <t>$                 $                                                                                                    Shareholders'  Deficiency                    (84,369,289)$    555,370</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>432,242   12,124                         555,370                                                                                                                                                                                                        1,480,006                                                                                                                         Shareholders'  Deficiency                    (76,712,652)$                                      (8,101,003)      (84,369,289)$                                           (10,830,342)      (93,164,255)$</t>
+          <t>- -      (10,830,342)     (877,518,673) - -      (11,600,198)     (889,118,871)                                                              Deficit                      (866,688,331)</t>
         </is>
       </c>
       <c r="D394" t="inlineStr"/>
@@ -45876,12 +45830,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>WEIGHTED AVERAGE NUMBER OF SHARES</t>
+          <t>$                 $                                                                                                    Shareholders'  Deficiency                    (84,369,289)$    555,370</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Non- controlling interests (19,669,467)</t>
+          <t>surplus 756,624 66,753,692</t>
         </is>
       </c>
       <c r="D395" t="inlineStr"/>
@@ -45920,16 +45874,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L395" s="5" t="n">
-        <v>-19.669467</v>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M395" s="5" t="n">
-        <v>-19.669467</v>
-      </c>
-      <c r="N395" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>65.997068</v>
+      </c>
+      <c r="N395" s="5" t="n">
+        <v>1.480006</v>
       </c>
       <c r="O395" t="inlineStr">
         <is>
@@ -45970,12 +45924,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>WEIGHTED AVERAGE NUMBER OF SHARES</t>
+          <t>OPERATING EXPENSES</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Deficit (858,587,328) (8,101,003) (866,688,331)</t>
+          <t>Loss on revaluation of gold sale contract (Note 5)</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
@@ -46015,10 +45969,10 @@
         </is>
       </c>
       <c r="L396" s="5" t="n">
-        <v>-877.518673</v>
+        <v>0.603757</v>
       </c>
       <c r="M396" s="5" t="n">
-        <v>-10.830342</v>
+        <v>1.743214</v>
       </c>
       <c r="N396" t="inlineStr">
         <is>
@@ -46064,12 +46018,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>WEIGHTED AVERAGE NUMBER OF SHARES</t>
+          <t>OPERATING EXPENSES</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>12,124 surplus (307,034)</t>
+          <t>Increase in decommissioning and restoration provision (Note 6)</t>
         </is>
       </c>
       <c r="D397" t="inlineStr"/>
@@ -46109,10 +46063,10 @@
         </is>
       </c>
       <c r="L397" s="5" t="n">
-        <v>65.997068</v>
+        <v>1.915058</v>
       </c>
       <c r="M397" s="5" t="n">
-        <v>1.480006</v>
+        <v>2.812516</v>
       </c>
       <c r="N397" t="inlineStr">
         <is>
@@ -46158,15 +46112,19 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>$                                                                                                      Contributed                            65,158,974$                                                 64,864,064$      (347,002)</t>
+          <t>OPERATING EXPENSES</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>$                                                                                                      Contributed                            65,158,974$                                                 64,864,064$      (347,002)</t>
-        </is>
-      </c>
-      <c r="D398" t="inlineStr"/>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E398" t="inlineStr">
         <is>
           <t>-</t>
@@ -46202,10 +46160,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L398" s="5" t="n">
+        <v>-0.05</v>
       </c>
       <c r="M398" t="inlineStr">
         <is>
@@ -46261,14 +46217,10 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>INCOME (LOSS) FROM OPERATIONS</t>
-        </is>
-      </c>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Gain on transfer of convertible loan (Note 7)</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr"/>
       <c r="E399" t="inlineStr">
         <is>
           <t>-</t>
@@ -46299,16 +46251,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K399" s="5" t="n">
-        <v>-0.61713</v>
-      </c>
-      <c r="L399" s="5" t="n">
-        <v>-1.746761</v>
-      </c>
-      <c r="M399" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M399" s="5" t="n">
+        <v>-1.331691</v>
       </c>
       <c r="N399" t="inlineStr">
         <is>
@@ -46354,12 +46308,12 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Increase in decommissioning and restoration provision</t>
+          <t>OPERATING EXPENSES</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>(Note 6)</t>
+          <t>Foreign exchange gain on currency devaluation (Note 2(b))</t>
         </is>
       </c>
       <c r="D400" t="inlineStr"/>
@@ -46383,10 +46337,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I400" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I400" s="5" t="n">
+        <v>-33.078</v>
       </c>
       <c r="J400" t="inlineStr">
         <is>
@@ -46394,15 +46346,13 @@
         </is>
       </c>
       <c r="K400" s="5" t="n">
-        <v>14.348439</v>
+        <v>-93.822</v>
       </c>
       <c r="L400" s="5" t="n">
-        <v>1.915058</v>
-      </c>
-      <c r="M400" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.520758</v>
+      </c>
+      <c r="M400" s="5" t="n">
+        <v>-3.422349</v>
       </c>
       <c r="N400" t="inlineStr">
         <is>
@@ -46448,17 +46398,17 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Increase in decommissioning and restoration provision</t>
+          <t>OPERATING EXPENSES</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>OPERATING EXPENSES total</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -46481,28 +46431,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I401" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J401" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K401" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I401" s="5" t="n">
+        <v>2.055</v>
+      </c>
+      <c r="J401" s="5" t="n">
+        <v>1.243</v>
+      </c>
+      <c r="K401" s="5" t="n">
+        <v>0.617</v>
       </c>
       <c r="L401" s="5" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="M401" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.354242</v>
+      </c>
+      <c r="M401" s="5" t="n">
+        <v>7.762497</v>
       </c>
       <c r="N401" t="inlineStr">
         <is>
@@ -46548,15 +46490,19 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Increase in decommissioning and restoration provision</t>
+          <t>OPERATING EXPENSES</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Foreign exchange gain on currency devaluation (Note 2(b))</t>
-        </is>
-      </c>
-      <c r="D402" t="inlineStr"/>
+          <t>NET LOSS AND COMPREHENSIVE LOSS</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E402" t="inlineStr">
         <is>
           <t>-</t>
@@ -46587,16 +46533,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K402" s="5" t="n">
-        <v>-93.821703</v>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L402" s="5" t="n">
-        <v>-3.520758</v>
-      </c>
-      <c r="M402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-8.101003</v>
+      </c>
+      <c r="M402" s="5" t="n">
+        <v>-10.830342</v>
       </c>
       <c r="N402" t="inlineStr">
         <is>
@@ -46642,12 +46588,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Increase in decommissioning and restoration provision</t>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Increase in decommissioning and restoration provision total</t>
+          <t>432,242   12,124                         555,370                                                                                                                                                                                                        1,480,006                                                                                                                         Shareholders'  Deficiency                    (76,712,652)$                                      (8,101,003)      (84,369,289)$                                           (10,830,342)      (93,164,255)$</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
@@ -46681,11 +46627,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K403" s="5" t="n">
-        <v>-74.336951</v>
-      </c>
-      <c r="L403" s="5" t="n">
-        <v>6.354242</v>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M403" t="inlineStr">
         <is>
@@ -46736,12 +46686,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>NET INCOME (LOSS) AND COMPREHENSIVE INCOME</t>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>(LOSS)</t>
+          <t>Non- controlling interests (19,669,467)</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
@@ -46775,16 +46725,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K404" s="5" t="n">
-        <v>73.719821</v>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L404" s="5" t="n">
-        <v>-8.101003</v>
-      </c>
-      <c r="M404" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-19.669467</v>
+      </c>
+      <c r="M404" s="5" t="n">
+        <v>-19.669467</v>
       </c>
       <c r="N404" t="inlineStr">
         <is>
@@ -46830,19 +46780,15 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>INCOME (LOSS) PER SHARE</t>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Basic and diluted (Note 18) $</t>
-        </is>
-      </c>
-      <c r="D405" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Deficit (858,587,328) (8,101,003) (866,688,331)</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr"/>
       <c r="E405" t="inlineStr">
         <is>
           <t>-</t>
@@ -46873,16 +46819,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K405" s="5" t="n">
-        <v>1.4e-07</v>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L405" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="M405" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-877.518673</v>
+      </c>
+      <c r="M405" s="5" t="n">
+        <v>-10.830342</v>
       </c>
       <c r="N405" t="inlineStr">
         <is>
@@ -46928,12 +46874,12 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>OPERATING EXPENSES</t>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>General and administrative, net of recoveries (Note 10)</t>
+          <t>12,124 surplus (307,034)</t>
         </is>
       </c>
       <c r="D406" t="inlineStr"/>
@@ -46957,24 +46903,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I406" s="5" t="n">
-        <v>2.109</v>
-      </c>
-      <c r="J406" s="5" t="n">
-        <v>1.363</v>
-      </c>
-      <c r="K406" s="5" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="L406" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M406" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L406" s="5" t="n">
+        <v>65.997068</v>
+      </c>
+      <c r="M406" s="5" t="n">
+        <v>1.480006</v>
       </c>
       <c r="N406" t="inlineStr">
         <is>
@@ -47020,12 +46968,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>OPERATING EXPENSES</t>
+          <t>$                                                                                                      Contributed                            65,158,974$                                                 64,864,064$      (347,002)</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Interest on convertible loan (Note 8)</t>
+          <t>$                                                                                                      Contributed                            65,158,974$                                                 64,864,064$      (347,002)</t>
         </is>
       </c>
       <c r="D407" t="inlineStr"/>
@@ -47054,11 +47002,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J407" s="5" t="n">
-        <v>4.651</v>
-      </c>
-      <c r="K407" s="5" t="n">
-        <v>5.184</v>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L407" t="inlineStr">
         <is>
@@ -47119,10 +47071,14 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Interest on gold sale contract (Note 6)</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr"/>
+          <t>INCOME (LOSS) FROM OPERATIONS</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
           <t>-</t>
@@ -47143,19 +47099,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I408" s="5" t="n">
-        <v>0.646</v>
-      </c>
-      <c r="J408" s="5" t="n">
-        <v>1.127</v>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K408" s="5" t="n">
-        <v>0.762</v>
-      </c>
-      <c r="L408" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.61713</v>
+      </c>
+      <c r="L408" s="5" t="n">
+        <v>-1.746761</v>
       </c>
       <c r="M408" t="inlineStr">
         <is>
@@ -47206,12 +47164,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>OPERATING EXPENSES</t>
+          <t>Increase in decommissioning and restoration provision</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Gain on revaluation of gold sale contract (Note 6)</t>
+          <t>(Note 6)</t>
         </is>
       </c>
       <c r="D409" t="inlineStr"/>
@@ -47235,19 +47193,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I409" s="5" t="n">
-        <v>-3.009</v>
-      </c>
-      <c r="J409" s="5" t="n">
-        <v>-0.143</v>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K409" s="5" t="n">
-        <v>-0.8090000000000001</v>
-      </c>
-      <c r="L409" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>14.348439</v>
+      </c>
+      <c r="L409" s="5" t="n">
+        <v>1.915058</v>
       </c>
       <c r="M409" t="inlineStr">
         <is>
@@ -47298,15 +47258,19 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>OPERATING EXPENSES</t>
+          <t>Increase in decommissioning and restoration provision</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Increase in rehabilitation provision (Note 7)</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr"/>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E410" t="inlineStr">
         <is>
           <t>-</t>
@@ -47332,16 +47296,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J410" s="5" t="n">
-        <v>7.061</v>
-      </c>
-      <c r="K410" s="5" t="n">
-        <v>14.348</v>
-      </c>
-      <c r="L410" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L410" s="5" t="n">
+        <v>-0.05</v>
       </c>
       <c r="M410" t="inlineStr">
         <is>
@@ -47392,19 +47358,15 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>OPERATING EXPENSES</t>
+          <t>Increase in decommissioning and restoration provision</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>NET INCOME (LOSS) AND COMPREHENSIVE</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Foreign exchange gain on currency devaluation (Note 2(b))</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr"/>
       <c r="E411" t="inlineStr">
         <is>
           <t>-</t>
@@ -47430,16 +47392,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J411" s="5" t="n">
-        <v>-13.939</v>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K411" s="5" t="n">
-        <v>73.72</v>
-      </c>
-      <c r="L411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-93.821703</v>
+      </c>
+      <c r="L411" s="5" t="n">
+        <v>-3.520758</v>
       </c>
       <c r="M411" t="inlineStr">
         <is>
@@ -47490,19 +47452,15 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>EARNINGS (LOSS) PER SHARE</t>
+          <t>Increase in decommissioning and restoration provision</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Basic and diluted (Note 18) $</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Increase in decommissioning and restoration provision total</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr">
         <is>
           <t>-</t>
@@ -47523,19 +47481,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I412" s="5" t="n">
-        <v>5e-08</v>
-      </c>
-      <c r="J412" s="5" t="n">
-        <v>-3e-08</v>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K412" s="5" t="n">
-        <v>1.4e-07</v>
-      </c>
-      <c r="L412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-74.336951</v>
+      </c>
+      <c r="L412" s="5" t="n">
+        <v>6.354242</v>
       </c>
       <c r="M412" t="inlineStr">
         <is>
@@ -47586,12 +47546,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>OUTSTANDING</t>
+          <t>NET INCOME (LOSS) AND COMPREHENSIVE INCOME</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>(LOSS)</t>
         </is>
       </c>
       <c r="D413" t="inlineStr"/>
@@ -47615,19 +47575,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I413" s="5" t="n">
-        <v>532.621</v>
-      </c>
-      <c r="J413" s="5" t="n">
-        <v>532.621</v>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K413" s="5" t="n">
-        <v>532.621</v>
-      </c>
-      <c r="L413" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>73.719821</v>
+      </c>
+      <c r="L413" s="5" t="n">
+        <v>-8.101003</v>
       </c>
       <c r="M413" t="inlineStr">
         <is>
@@ -47678,15 +47640,19 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>OUTSTANDING</t>
+          <t>INCOME (LOSS) PER SHARE</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Diluted</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr"/>
+          <t>Basic and diluted (Note 18) $</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E414" t="inlineStr">
         <is>
           <t>-</t>
@@ -47707,19 +47673,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I414" s="5" t="n">
-        <v>532.621</v>
-      </c>
-      <c r="J414" s="5" t="n">
-        <v>532.621</v>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K414" s="5" t="n">
-        <v>532.621</v>
-      </c>
-      <c r="L414" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.4e-07</v>
+      </c>
+      <c r="L414" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="M414" t="inlineStr">
         <is>
@@ -47775,7 +47743,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Share based compensation</t>
+          <t>General and administrative, net of recoveries (Note 10)</t>
         </is>
       </c>
       <c r="D415" t="inlineStr"/>
@@ -47800,17 +47768,13 @@
         </is>
       </c>
       <c r="I415" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J415" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K415" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.109</v>
+      </c>
+      <c r="J415" s="5" t="n">
+        <v>1.363</v>
+      </c>
+      <c r="K415" s="5" t="n">
+        <v>0.8100000000000001</v>
       </c>
       <c r="L415" t="inlineStr">
         <is>
@@ -47871,7 +47835,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Interest on convertible loan</t>
+          <t>Interest on convertible loan (Note 8)</t>
         </is>
       </c>
       <c r="D416" t="inlineStr"/>
@@ -47895,16 +47859,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I416" s="5" t="n">
-        <v>4.173</v>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J416" s="5" t="n">
         <v>4.651</v>
       </c>
-      <c r="K416" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K416" s="5" t="n">
+        <v>5.184</v>
       </c>
       <c r="L416" t="inlineStr">
         <is>
@@ -47965,7 +47929,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Recovery of Value Added Taxes, net of fees</t>
+          <t>Interest on gold sale contract (Note 6)</t>
         </is>
       </c>
       <c r="D417" t="inlineStr"/>
@@ -47990,17 +47954,13 @@
         </is>
       </c>
       <c r="I417" s="5" t="n">
-        <v>-1.046</v>
-      </c>
-      <c r="J417" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K417" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.646</v>
+      </c>
+      <c r="J417" s="5" t="n">
+        <v>1.127</v>
+      </c>
+      <c r="K417" s="5" t="n">
+        <v>0.762</v>
       </c>
       <c r="L417" t="inlineStr">
         <is>
@@ -48061,7 +48021,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Increase in rehabilitation provision</t>
+          <t>Gain on revaluation of gold sale contract (Note 6)</t>
         </is>
       </c>
       <c r="D418" t="inlineStr"/>
@@ -48086,15 +48046,13 @@
         </is>
       </c>
       <c r="I418" s="5" t="n">
-        <v>4.378</v>
+        <v>-3.009</v>
       </c>
       <c r="J418" s="5" t="n">
-        <v>7.061</v>
-      </c>
-      <c r="K418" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.143</v>
+      </c>
+      <c r="K418" s="5" t="n">
+        <v>-0.8090000000000001</v>
       </c>
       <c r="L418" t="inlineStr">
         <is>
@@ -48150,19 +48108,15 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Attributable to</t>
+          <t>OPERATING EXPENSES</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Non-controlling interests</t>
-        </is>
-      </c>
-      <c r="D419" t="inlineStr">
-        <is>
-          <t>MinorityInterests</t>
-        </is>
-      </c>
+          <t>Increase in rehabilitation provision (Note 7)</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
@@ -48173,24 +48127,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G419" s="5" t="n">
-        <v>22.343</v>
-      </c>
-      <c r="H419" s="5" t="n">
-        <v>0.588</v>
-      </c>
-      <c r="I419" s="5" t="n">
-        <v>-1.24</v>
-      </c>
-      <c r="J419" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K419" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J419" s="5" t="n">
+        <v>7.061</v>
+      </c>
+      <c r="K419" s="5" t="n">
+        <v>14.348</v>
       </c>
       <c r="L419" t="inlineStr">
         <is>
@@ -48244,13 +48200,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B420" t="inlineStr"/>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES</t>
+        </is>
+      </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>REVENUES FROM MINING OPERATIONS $</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr"/>
+          <t>NET INCOME (LOSS) AND COMPREHENSIVE</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E420" t="inlineStr">
         <is>
           <t>-</t>
@@ -48266,23 +48230,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H420" s="5" t="n">
-        <v>4.926</v>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I420" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J420" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K420" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J420" s="5" t="n">
+        <v>-13.939</v>
+      </c>
+      <c r="K420" s="5" t="n">
+        <v>73.72</v>
       </c>
       <c r="L420" t="inlineStr">
         <is>
@@ -48338,17 +48300,17 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>COSTS OF MINING OPERATIONS</t>
+          <t>EARNINGS (LOSS) PER SHARE</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Mining operating expenses (Note 10)</t>
+          <t>Basic and diluted (Note 18) $</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -48366,23 +48328,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H421" s="5" t="n">
-        <v>25.256</v>
-      </c>
-      <c r="I421" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J421" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K421" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I421" s="5" t="n">
+        <v>5e-08</v>
+      </c>
+      <c r="J421" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="K421" s="5" t="n">
+        <v>1.4e-07</v>
       </c>
       <c r="L421" t="inlineStr">
         <is>
@@ -48438,12 +48396,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>COSTS OF MINING OPERATIONS</t>
+          <t>OUTSTANDING</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>LOSS FROM MINING OPERATIONS</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="D422" t="inlineStr"/>
@@ -48457,26 +48415,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G422" s="5" t="n">
-        <v>-53.982</v>
-      </c>
-      <c r="H422" s="5" t="n">
-        <v>-20.33</v>
-      </c>
-      <c r="I422" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J422" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K422" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I422" s="5" t="n">
+        <v>532.621</v>
+      </c>
+      <c r="J422" s="5" t="n">
+        <v>532.621</v>
+      </c>
+      <c r="K422" s="5" t="n">
+        <v>532.621</v>
       </c>
       <c r="L422" t="inlineStr">
         <is>
@@ -48532,12 +48488,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>COSTS OF MINING OPERATIONS</t>
+          <t>OUTSTANDING</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Share-based compensation expense</t>
+          <t>Diluted</t>
         </is>
       </c>
       <c r="D423" t="inlineStr"/>
@@ -48551,24 +48507,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G423" s="5" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="H423" s="5" t="n">
-        <v>0.827</v>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I423" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J423" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K423" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>532.621</v>
+      </c>
+      <c r="J423" s="5" t="n">
+        <v>532.621</v>
+      </c>
+      <c r="K423" s="5" t="n">
+        <v>532.621</v>
       </c>
       <c r="L423" t="inlineStr">
         <is>
@@ -48624,12 +48580,12 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>COSTS OF MINING OPERATIONS</t>
+          <t>OPERATING EXPENSES</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>General and administrative, net of recoveries (Note 11)</t>
+          <t>Share based compensation</t>
         </is>
       </c>
       <c r="D424" t="inlineStr"/>
@@ -48648,11 +48604,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H424" s="5" t="n">
-        <v>5.883</v>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I424" s="5" t="n">
-        <v>2.109</v>
+        <v>0.15</v>
       </c>
       <c r="J424" t="inlineStr">
         <is>
@@ -48718,19 +48676,15 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>COSTS OF MINING OPERATIONS</t>
+          <t>OPERATING EXPENSES</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Foreign exchange (gain) loss</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Interest on convertible loan</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr"/>
       <c r="E425" t="inlineStr">
         <is>
           <t>-</t>
@@ -48746,16 +48700,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H425" s="5" t="n">
-        <v>1.023</v>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I425" s="5" t="n">
-        <v>-0.204</v>
-      </c>
-      <c r="J425" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.173</v>
+      </c>
+      <c r="J425" s="5" t="n">
+        <v>4.651</v>
       </c>
       <c r="K425" t="inlineStr">
         <is>
@@ -48816,12 +48770,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>COSTS OF MINING OPERATIONS</t>
+          <t>OPERATING EXPENSES</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>COSTS OF MINING OPERATIONS total</t>
+          <t>Recovery of Value Added Taxes, net of fees</t>
         </is>
       </c>
       <c r="D426" t="inlineStr"/>
@@ -48835,14 +48789,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G426" s="5" t="n">
-        <v>161.315</v>
-      </c>
-      <c r="H426" s="5" t="n">
-        <v>7.733</v>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I426" s="5" t="n">
-        <v>2.055</v>
+        <v>-1.046</v>
       </c>
       <c r="J426" t="inlineStr">
         <is>
@@ -48908,19 +48866,15 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>COSTS OF MINING OPERATIONS</t>
+          <t>OPERATING EXPENSES</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>LOSS FROM OPERATIONS</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Increase in rehabilitation provision</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr"/>
       <c r="E427" t="inlineStr">
         <is>
           <t>-</t>
@@ -48931,19 +48885,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G427" s="5" t="n">
-        <v>-60.201</v>
-      </c>
-      <c r="H427" s="5" t="n">
-        <v>-28.063</v>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I427" s="5" t="n">
-        <v>-2.055</v>
-      </c>
-      <c r="J427" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.378</v>
+      </c>
+      <c r="J427" s="5" t="n">
+        <v>7.061</v>
       </c>
       <c r="K427" t="inlineStr">
         <is>
@@ -49004,15 +48960,19 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>COSTS OF MINING OPERATIONS</t>
+          <t>Attributable to</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Interest on convertible loan</t>
-        </is>
-      </c>
-      <c r="D428" t="inlineStr"/>
+          <t>Non-controlling interests</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
           <t>-</t>
@@ -49024,13 +48984,13 @@
         </is>
       </c>
       <c r="G428" s="5" t="n">
-        <v>4.594</v>
+        <v>22.343</v>
       </c>
       <c r="H428" s="5" t="n">
-        <v>3.753</v>
+        <v>0.588</v>
       </c>
       <c r="I428" s="5" t="n">
-        <v>4.173</v>
+        <v>-1.24</v>
       </c>
       <c r="J428" t="inlineStr">
         <is>
@@ -49094,14 +49054,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>COSTS OF MINING OPERATIONS</t>
-        </is>
-      </c>
+      <c r="B429" t="inlineStr"/>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Interest on gold sale contract (Note 6)</t>
+          <t>REVENUES FROM MINING OPERATIONS $</t>
         </is>
       </c>
       <c r="D429" t="inlineStr"/>
@@ -49121,10 +49077,12 @@
         </is>
       </c>
       <c r="H429" s="5" t="n">
-        <v>1.211</v>
-      </c>
-      <c r="I429" s="5" t="n">
-        <v>0.646</v>
+        <v>4.926</v>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J429" t="inlineStr">
         <is>
@@ -49195,10 +49153,14 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>(Gain) loss on revaluation of gold sale contract (Note 6)</t>
-        </is>
-      </c>
-      <c r="D430" t="inlineStr"/>
+          <t>Mining operating expenses (Note 10)</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E430" t="inlineStr">
         <is>
           <t>-</t>
@@ -49215,10 +49177,12 @@
         </is>
       </c>
       <c r="H430" s="5" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="I430" s="5" t="n">
-        <v>-3.009</v>
+        <v>25.256</v>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
@@ -49289,7 +49253,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Loss on repatriation of monetary assets</t>
+          <t>LOSS FROM MINING OPERATIONS</t>
         </is>
       </c>
       <c r="D431" t="inlineStr"/>
@@ -49303,13 +49267,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G431" s="5" t="n">
+        <v>-53.982</v>
       </c>
       <c r="H431" s="5" t="n">
-        <v>0.534</v>
+        <v>-20.33</v>
       </c>
       <c r="I431" t="inlineStr">
         <is>
@@ -49385,7 +49347,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Impairment loss on write-down of property plant and equipment and mineral properties</t>
+          <t>Share-based compensation expense</t>
         </is>
       </c>
       <c r="D432" t="inlineStr"/>
@@ -49399,18 +49361,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G432" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G432" s="5" t="n">
+        <v>0.014</v>
       </c>
       <c r="H432" s="5" t="n">
-        <v>4.019</v>
-      </c>
-      <c r="I432" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.827</v>
+      </c>
+      <c r="I432" s="5" t="n">
+        <v>0.15</v>
       </c>
       <c r="J432" t="inlineStr">
         <is>
@@ -49481,7 +49439,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Foreign exchange gain on currency devaluation</t>
+          <t>General and administrative, net of recoveries (Note 11)</t>
         </is>
       </c>
       <c r="D433" t="inlineStr"/>
@@ -49500,13 +49458,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H433" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H433" s="5" t="n">
+        <v>5.883</v>
       </c>
       <c r="I433" s="5" t="n">
-        <v>-33.078</v>
+        <v>2.109</v>
       </c>
       <c r="J433" t="inlineStr">
         <is>
@@ -49577,10 +49533,14 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Recovery of Value Added Taxes, net of fees (Note 4)</t>
-        </is>
-      </c>
-      <c r="D434" t="inlineStr"/>
+          <t>Foreign exchange (gain) loss</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E434" t="inlineStr">
         <is>
           <t>-</t>
@@ -49596,13 +49556,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H434" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H434" s="5" t="n">
+        <v>1.023</v>
       </c>
       <c r="I434" s="5" t="n">
-        <v>-1.046</v>
+        <v>-0.204</v>
       </c>
       <c r="J434" t="inlineStr">
         <is>
@@ -49673,7 +49631,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Increase in rehabilitation provision</t>
+          <t>COSTS OF MINING OPERATIONS total</t>
         </is>
       </c>
       <c r="D435" t="inlineStr"/>
@@ -49687,16 +49645,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G435" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G435" s="5" t="n">
+        <v>161.315</v>
       </c>
       <c r="H435" s="5" t="n">
-        <v>5.016</v>
+        <v>7.733</v>
       </c>
       <c r="I435" s="5" t="n">
-        <v>4.378</v>
+        <v>2.055</v>
       </c>
       <c r="J435" t="inlineStr">
         <is>
@@ -49767,10 +49723,14 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Litigation costs, net of recoveries (Note 11)</t>
-        </is>
-      </c>
-      <c r="D436" t="inlineStr"/>
+          <t>LOSS FROM OPERATIONS</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E436" t="inlineStr">
         <is>
           <t>-</t>
@@ -49781,18 +49741,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G436" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G436" s="5" t="n">
+        <v>-60.201</v>
       </c>
       <c r="H436" s="5" t="n">
-        <v>0.306</v>
-      </c>
-      <c r="I436" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-28.063</v>
+      </c>
+      <c r="I436" s="5" t="n">
+        <v>-2.055</v>
       </c>
       <c r="J436" t="inlineStr">
         <is>
@@ -49863,7 +49819,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Settlement of Gold Reserve litigation (Note 17)</t>
+          <t>Interest on convertible loan</t>
         </is>
       </c>
       <c r="D437" t="inlineStr"/>
@@ -49877,18 +49833,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G437" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G437" s="5" t="n">
+        <v>4.594</v>
       </c>
       <c r="H437" s="5" t="n">
-        <v>0.358</v>
-      </c>
-      <c r="I437" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.753</v>
+      </c>
+      <c r="I437" s="5" t="n">
+        <v>4.173</v>
       </c>
       <c r="J437" t="inlineStr">
         <is>
@@ -49959,14 +49911,10 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Other (income) expenses</t>
-        </is>
-      </c>
-      <c r="D438" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Interest on gold sale contract (Note 6)</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr"/>
       <c r="E438" t="inlineStr">
         <is>
           <t>-</t>
@@ -49977,16 +49925,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G438" s="5" t="n">
-        <v>-3.141</v>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H438" s="5" t="n">
-        <v>0.213</v>
-      </c>
-      <c r="I438" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.211</v>
+      </c>
+      <c r="I438" s="5" t="n">
+        <v>0.646</v>
       </c>
       <c r="J438" t="inlineStr">
         <is>
@@ -50057,14 +50005,10 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>NET INCOME (LOSS) AND COMPREHENSIVE INCOME (LOSS)</t>
-        </is>
-      </c>
-      <c r="D439" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>(Gain) loss on revaluation of gold sale contract (Note 6)</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr"/>
       <c r="E439" t="inlineStr">
         <is>
           <t>-</t>
@@ -50081,10 +50025,10 @@
         </is>
       </c>
       <c r="H439" s="5" t="n">
-        <v>-44.313</v>
+        <v>0.84</v>
       </c>
       <c r="I439" s="5" t="n">
-        <v>25.881</v>
+        <v>-3.009</v>
       </c>
       <c r="J439" t="inlineStr">
         <is>
@@ -50150,19 +50094,15 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>EARNINGS (LOSS) PER SHARE</t>
+          <t>COSTS OF MINING OPERATIONS</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Basic and diluted (Note 19) $</t>
-        </is>
-      </c>
-      <c r="D440" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Loss on repatriation of monetary assets</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr"/>
       <c r="E440" t="inlineStr">
         <is>
           <t>-</t>
@@ -50179,10 +50119,12 @@
         </is>
       </c>
       <c r="H440" s="5" t="n">
-        <v>-8e-08</v>
-      </c>
-      <c r="I440" s="5" t="n">
-        <v>5e-08</v>
+        <v>0.534</v>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J440" t="inlineStr">
         <is>
@@ -50248,19 +50190,15 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
+          <t>COSTS OF MINING OPERATIONS</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D441" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>Impairment loss on write-down of property plant and equipment and mineral properties</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr"/>
       <c r="E441" t="inlineStr">
         <is>
           <t>-</t>
@@ -50271,14 +50209,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G441" s="5" t="n">
-        <v>0.5301129999999999</v>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H441" s="5" t="n">
-        <v>0.530675</v>
-      </c>
-      <c r="I441" s="5" t="n">
-        <v>0.532621</v>
+        <v>4.019</v>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J441" t="inlineStr">
         <is>
@@ -50344,19 +50286,15 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
+          <t>COSTS OF MINING OPERATIONS</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Diluted</t>
-        </is>
-      </c>
-      <c r="D442" t="inlineStr">
-        <is>
-          <t>DilutedAverageShares</t>
-        </is>
-      </c>
+          <t>Foreign exchange gain on currency devaluation</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr"/>
       <c r="E442" t="inlineStr">
         <is>
           <t>-</t>
@@ -50367,14 +50305,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G442" s="5" t="n">
-        <v>0.5301129999999999</v>
-      </c>
-      <c r="H442" s="5" t="n">
-        <v>0.530675</v>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I442" s="5" t="n">
-        <v>0.532621</v>
+        <v>-33.078</v>
       </c>
       <c r="J442" t="inlineStr">
         <is>
@@ -50440,12 +50382,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
+          <t>COSTS OF MINING OPERATIONS</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>(899,284) - -  (43,725)   (943,009) -      24,641   (918,368)                                                             Deficit</t>
+          <t>Recovery of Value Added Taxes, net of fees (Note 4)</t>
         </is>
       </c>
       <c r="D443" t="inlineStr"/>
@@ -50464,13 +50406,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H443" s="5" t="n">
-        <v>65.15900000000001</v>
-      </c>
-      <c r="I443" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I443" s="5" t="n">
+        <v>-1.046</v>
       </c>
       <c r="J443" t="inlineStr">
         <is>
@@ -50536,12 +50478,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>surplus                                                                                        Contributed</t>
+          <t>COSTS OF MINING OPERATIONS</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>surplus                                                                                        Contributed    $           $</t>
+          <t>Increase in rehabilitation provision</t>
         </is>
       </c>
       <c r="D444" t="inlineStr"/>
@@ -50561,12 +50503,10 @@
         </is>
       </c>
       <c r="H444" s="5" t="n">
-        <v>736.385</v>
-      </c>
-      <c r="I444" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.016</v>
+      </c>
+      <c r="I444" s="5" t="n">
+        <v>4.378</v>
       </c>
       <c r="J444" t="inlineStr">
         <is>
@@ -50632,12 +50572,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>$           $                                                   capital</t>
+          <t>COSTS OF MINING OPERATIONS</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>$           $                                                   capital amounts) - - - - statements. Issued 2,500 share 530,121</t>
+          <t>Litigation costs, net of recoveries (Note 11)</t>
         </is>
       </c>
       <c r="D445" t="inlineStr"/>
@@ -50657,10 +50597,12 @@
         </is>
       </c>
       <c r="H445" s="5" t="n">
-        <v>532.621</v>
-      </c>
-      <c r="I445" s="5" t="n">
-        <v>532.621</v>
+        <v>0.306</v>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J445" t="inlineStr">
         <is>
@@ -50726,12 +50668,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>of of                                                   to</t>
+          <t>COSTS OF MINING OPERATIONS</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>31, 9(b))</t>
+          <t>Settlement of Gold Reserve litigation (Note 17)</t>
         </is>
       </c>
       <c r="D446" t="inlineStr"/>
@@ -50751,10 +50693,12 @@
         </is>
       </c>
       <c r="H446" s="5" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="I446" s="5" t="n">
-        <v>0.031</v>
+        <v>0.358</v>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J446" t="inlineStr">
         <is>
@@ -50818,13 +50762,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B447" t="inlineStr"/>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>COSTS OF MINING OPERATIONS</t>
+        </is>
+      </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>REVENUES FROM MINING OPERATIONS</t>
-        </is>
-      </c>
-      <c r="D447" t="inlineStr"/>
+          <t>Other (income) expenses</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E447" t="inlineStr">
         <is>
           <t>-</t>
@@ -50836,10 +50788,10 @@
         </is>
       </c>
       <c r="G447" s="5" t="n">
-        <v>107.333</v>
+        <v>-3.141</v>
       </c>
       <c r="H447" s="5" t="n">
-        <v>4.926</v>
+        <v>0.213</v>
       </c>
       <c r="I447" t="inlineStr">
         <is>
@@ -50915,12 +50867,12 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Mining operating expenses (Notes 15 and 17)</t>
+          <t>NET INCOME (LOSS) AND COMPREHENSIVE INCOME (LOSS)</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -50933,16 +50885,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G448" s="5" t="n">
-        <v>147.935</v>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H448" s="5" t="n">
-        <v>25.256</v>
-      </c>
-      <c r="I448" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-44.313</v>
+      </c>
+      <c r="I448" s="5" t="n">
+        <v>25.881</v>
       </c>
       <c r="J448" t="inlineStr">
         <is>
@@ -51008,15 +50960,19 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>COSTS OF MINING OPERATIONS</t>
+          <t>EARNINGS (LOSS) PER SHARE</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Depreciation and depletion</t>
-        </is>
-      </c>
-      <c r="D449" t="inlineStr"/>
+          <t>Basic and diluted (Note 19) $</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E449" t="inlineStr">
         <is>
           <t>-</t>
@@ -51027,18 +50983,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G449" s="5" t="n">
-        <v>13.38</v>
-      </c>
-      <c r="H449" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I449" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H449" s="5" t="n">
+        <v>-8e-08</v>
+      </c>
+      <c r="I449" s="5" t="n">
+        <v>5e-08</v>
       </c>
       <c r="J449" t="inlineStr">
         <is>
@@ -51104,15 +51058,19 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>COSTS OF MINING OPERATIONS</t>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>General and administrative, net of recoveries (Note 16)</t>
-        </is>
-      </c>
-      <c r="D450" t="inlineStr"/>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E450" t="inlineStr">
         <is>
           <t>-</t>
@@ -51124,15 +51082,13 @@
         </is>
       </c>
       <c r="G450" s="5" t="n">
-        <v>6.603</v>
+        <v>0.5301129999999999</v>
       </c>
       <c r="H450" s="5" t="n">
-        <v>5.883</v>
-      </c>
-      <c r="I450" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.530675</v>
+      </c>
+      <c r="I450" s="5" t="n">
+        <v>0.532621</v>
       </c>
       <c r="J450" t="inlineStr">
         <is>
@@ -51198,17 +51154,17 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>COSTS OF MINING OPERATIONS</t>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss)</t>
+          <t>Diluted</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>DilutedAverageShares</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -51222,15 +51178,13 @@
         </is>
       </c>
       <c r="G451" s="5" t="n">
-        <v>-0.398</v>
+        <v>0.5301129999999999</v>
       </c>
       <c r="H451" s="5" t="n">
-        <v>1.023</v>
-      </c>
-      <c r="I451" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.530675</v>
+      </c>
+      <c r="I451" s="5" t="n">
+        <v>0.532621</v>
       </c>
       <c r="J451" t="inlineStr">
         <is>
@@ -51296,12 +51250,12 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>COSTS OF MINING OPERATIONS</t>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Interest on gold sale contract (Note 10b)</t>
+          <t>(899,284) - -  (43,725)   (943,009) -      24,641   (918,368)                                                             Deficit</t>
         </is>
       </c>
       <c r="D452" t="inlineStr"/>
@@ -51321,7 +51275,7 @@
         </is>
       </c>
       <c r="H452" s="5" t="n">
-        <v>1.211</v>
+        <v>65.15900000000001</v>
       </c>
       <c r="I452" t="inlineStr">
         <is>
@@ -51392,12 +51346,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>COSTS OF MINING OPERATIONS</t>
+          <t>surplus                                                                                        Contributed</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Loss (gain) on revaluation of derivative financial liabilities</t>
+          <t>surplus                                                                                        Contributed    $           $</t>
         </is>
       </c>
       <c r="D453" t="inlineStr"/>
@@ -51411,13 +51365,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G453" s="5" t="n">
-        <v>-4.103</v>
-      </c>
-      <c r="H453" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H453" s="5" t="n">
+        <v>736.385</v>
       </c>
       <c r="I453" t="inlineStr">
         <is>
@@ -51488,12 +51442,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>COSTS OF MINING OPERATIONS</t>
+          <t>$           $                                                   capital</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Loss on revaluation of gold sale contract (Note 10b)</t>
+          <t>$           $                                                   capital amounts) - - - - statements. Issued 2,500 share 530,121</t>
         </is>
       </c>
       <c r="D454" t="inlineStr"/>
@@ -51507,16 +51461,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G454" s="5" t="n">
-        <v>4.237</v>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H454" s="5" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="I454" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>532.621</v>
+      </c>
+      <c r="I454" s="5" t="n">
+        <v>532.621</v>
       </c>
       <c r="J454" t="inlineStr">
         <is>
@@ -51582,12 +51536,12 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>COSTS OF MINING OPERATIONS</t>
+          <t>of of                                                   to</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Impairment loss on write-down of property plant and equipment and mineral properties (Notes 7 and 8)</t>
+          <t>31, 9(b))</t>
         </is>
       </c>
       <c r="D455" t="inlineStr"/>
@@ -51601,16 +51555,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G455" s="5" t="n">
-        <v>924.349</v>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H455" s="5" t="n">
-        <v>4.019</v>
-      </c>
-      <c r="I455" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.031</v>
+      </c>
+      <c r="I455" s="5" t="n">
+        <v>0.031</v>
       </c>
       <c r="J455" t="inlineStr">
         <is>
@@ -51674,14 +51628,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B456" t="inlineStr">
-        <is>
-          <t>COSTS OF MINING OPERATIONS</t>
-        </is>
-      </c>
+      <c r="B456" t="inlineStr"/>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Litigation costs, net of recoveries (Note 16)</t>
+          <t>REVENUES FROM MINING OPERATIONS</t>
         </is>
       </c>
       <c r="D456" t="inlineStr"/>
@@ -51695,13 +51645,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G456" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G456" s="5" t="n">
+        <v>107.333</v>
       </c>
       <c r="H456" s="5" t="n">
-        <v>0.306</v>
+        <v>4.926</v>
       </c>
       <c r="I456" t="inlineStr">
         <is>
@@ -51777,10 +51725,14 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Settlement of Gold Reserve litigation (Note 23)</t>
-        </is>
-      </c>
-      <c r="D457" t="inlineStr"/>
+          <t>Mining operating expenses (Notes 15 and 17)</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E457" t="inlineStr">
         <is>
           <t>-</t>
@@ -51791,13 +51743,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G457" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G457" s="5" t="n">
+        <v>147.935</v>
       </c>
       <c r="H457" s="5" t="n">
-        <v>0.358</v>
+        <v>25.256</v>
       </c>
       <c r="I457" t="inlineStr">
         <is>
@@ -51873,14 +51823,10 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>LOSS BEFORE INCOME TAXES</t>
-        </is>
-      </c>
-      <c r="D458" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Depreciation and depletion</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr"/>
       <c r="E458" t="inlineStr">
         <is>
           <t>-</t>
@@ -51892,10 +51838,12 @@
         </is>
       </c>
       <c r="G458" s="5" t="n">
-        <v>-986.1369999999999</v>
-      </c>
-      <c r="H458" s="5" t="n">
-        <v>-44.313</v>
+        <v>13.38</v>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I458" t="inlineStr">
         <is>
@@ -51971,7 +51919,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Current tax expense (Note 20)</t>
+          <t>General and administrative, net of recoveries (Note 16)</t>
         </is>
       </c>
       <c r="D459" t="inlineStr"/>
@@ -51986,12 +51934,10 @@
         </is>
       </c>
       <c r="G459" s="5" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="H459" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.603</v>
+      </c>
+      <c r="H459" s="5" t="n">
+        <v>5.883</v>
       </c>
       <c r="I459" t="inlineStr">
         <is>
@@ -52067,10 +52013,14 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Deferred tax recovery (Note 20)</t>
-        </is>
-      </c>
-      <c r="D460" t="inlineStr"/>
+          <t>Foreign exchange gain (loss)</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E460" t="inlineStr">
         <is>
           <t>-</t>
@@ -52082,12 +52032,10 @@
         </is>
       </c>
       <c r="G460" s="5" t="n">
-        <v>-206.021</v>
-      </c>
-      <c r="H460" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.398</v>
+      </c>
+      <c r="H460" s="5" t="n">
+        <v>1.023</v>
       </c>
       <c r="I460" t="inlineStr">
         <is>
@@ -52163,14 +52111,10 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>NET LOSS AND COMPREHENSIVE LOSS</t>
-        </is>
-      </c>
-      <c r="D461" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Interest on gold sale contract (Note 10b)</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr"/>
       <c r="E461" t="inlineStr">
         <is>
           <t>-</t>
@@ -52181,11 +52125,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G461" s="5" t="n">
-        <v>-780.1369999999999</v>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H461" s="5" t="n">
-        <v>-44.313</v>
+        <v>1.211</v>
       </c>
       <c r="I461" t="inlineStr">
         <is>
@@ -52256,19 +52202,15 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>LOSS PER SHARE</t>
+          <t>COSTS OF MINING OPERATIONS</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Basic and diluted (Note 25)</t>
-        </is>
-      </c>
-      <c r="D462" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Loss (gain) on revaluation of derivative financial liabilities</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr"/>
       <c r="E462" t="inlineStr">
         <is>
           <t>-</t>
@@ -52280,10 +52222,12 @@
         </is>
       </c>
       <c r="G462" s="5" t="n">
-        <v>-1.43e-06</v>
-      </c>
-      <c r="H462" s="5" t="n">
-        <v>-8e-08</v>
+        <v>-4.103</v>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I462" t="inlineStr">
         <is>
@@ -52354,12 +52298,12 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
+          <t>COSTS OF MINING OPERATIONS</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Equity $660,962 - 14 20 - (780,137) ($119,141)</t>
+          <t>Loss on revaluation of gold sale contract (Note 10b)</t>
         </is>
       </c>
       <c r="D463" t="inlineStr"/>
@@ -52374,10 +52318,10 @@
         </is>
       </c>
       <c r="G463" s="5" t="n">
-        <v>-162.525</v>
+        <v>4.237</v>
       </c>
       <c r="H463" s="5" t="n">
-        <v>-44.313</v>
+        <v>0.84</v>
       </c>
       <c r="I463" t="inlineStr">
         <is>
@@ -52448,12 +52392,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
+          <t>COSTS OF MINING OPERATIONS</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Deficit ($141,490) - - - - (757,794) ($899,284) - -</t>
+          <t>Impairment loss on write-down of property plant and equipment and mineral properties (Notes 7 and 8)</t>
         </is>
       </c>
       <c r="D464" t="inlineStr"/>
@@ -52468,10 +52412,10 @@
         </is>
       </c>
       <c r="G464" s="5" t="n">
-        <v>-943.009</v>
+        <v>924.349</v>
       </c>
       <c r="H464" s="5" t="n">
-        <v>-43.725</v>
+        <v>4.019</v>
       </c>
       <c r="I464" t="inlineStr">
         <is>
@@ -52540,32 +52484,34 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B465" t="inlineStr"/>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>COSTS OF MINING OPERATIONS</t>
+        </is>
+      </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>REVENUES</t>
-        </is>
-      </c>
-      <c r="D465" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E465" s="5" t="n">
-        <v>70.28700000000001</v>
-      </c>
-      <c r="F465" s="5" t="n">
-        <v>72.373</v>
+          <t>Litigation costs, net of recoveries (Note 16)</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr"/>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G465" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H465" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H465" s="5" t="n">
+        <v>0.306</v>
       </c>
       <c r="I465" t="inlineStr">
         <is>
@@ -52636,34 +52582,32 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>COSTS AND EXPENSES</t>
+          <t>COSTS OF MINING OPERATIONS</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Mining operating expenses</t>
-        </is>
-      </c>
-      <c r="D466" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E466" s="5" t="n">
-        <v>63.896</v>
-      </c>
-      <c r="F466" s="5" t="n">
-        <v>39.39</v>
+          <t>Settlement of Gold Reserve litigation (Note 23)</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr"/>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G466" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H466" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H466" s="5" t="n">
+        <v>0.358</v>
       </c>
       <c r="I466" t="inlineStr">
         <is>
@@ -52734,34 +52678,34 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>COSTS AND EXPENSES</t>
+          <t>COSTS OF MINING OPERATIONS</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Mining amortization</t>
+          <t>LOSS BEFORE INCOME TAXES</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="E467" s="5" t="n">
-        <v>17.544</v>
-      </c>
-      <c r="F467" s="5" t="n">
-        <v>10.225</v>
-      </c>
-      <c r="G467" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H467" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G467" s="5" t="n">
+        <v>-986.1369999999999</v>
+      </c>
+      <c r="H467" s="5" t="n">
+        <v>-44.313</v>
       </c>
       <c r="I467" t="inlineStr">
         <is>
@@ -52832,29 +52776,27 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>COSTS AND EXPENSES</t>
+          <t>COSTS OF MINING OPERATIONS</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>COSTS AND EXPENSES total</t>
-        </is>
-      </c>
-      <c r="D468" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E468" s="5" t="n">
-        <v>81.44</v>
-      </c>
-      <c r="F468" s="5" t="n">
-        <v>49.615</v>
-      </c>
-      <c r="G468" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Current tax expense (Note 20)</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr"/>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G468" s="5" t="n">
+        <v>0.021</v>
       </c>
       <c r="H468" t="inlineStr">
         <is>
@@ -52930,25 +52872,27 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>COSTS AND EXPENSES</t>
+          <t>COSTS OF MINING OPERATIONS</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>INCOME (LOSS) FROM MINING OPERATIONS</t>
+          <t>Deferred tax recovery (Note 20)</t>
         </is>
       </c>
       <c r="D469" t="inlineStr"/>
-      <c r="E469" s="5" t="n">
-        <v>-11.153</v>
-      </c>
-      <c r="F469" s="5" t="n">
-        <v>22.758</v>
-      </c>
-      <c r="G469" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G469" s="5" t="n">
+        <v>-206.021</v>
       </c>
       <c r="H469" t="inlineStr">
         <is>
@@ -53024,34 +52968,34 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>COSTS AND EXPENSES</t>
+          <t>COSTS OF MINING OPERATIONS</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>General and administrative (Note 14)</t>
+          <t>NET LOSS AND COMPREHENSIVE LOSS</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E470" s="5" t="n">
-        <v>19.741</v>
-      </c>
-      <c r="F470" s="5" t="n">
-        <v>9.355</v>
-      </c>
-      <c r="G470" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H470" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G470" s="5" t="n">
+        <v>-780.1369999999999</v>
+      </c>
+      <c r="H470" s="5" t="n">
+        <v>-44.313</v>
       </c>
       <c r="I470" t="inlineStr">
         <is>
@@ -53122,30 +53066,34 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>COSTS AND EXPENSES</t>
+          <t>LOSS PER SHARE</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Stock-based compensation (Note 12(b))</t>
-        </is>
-      </c>
-      <c r="D471" t="inlineStr"/>
-      <c r="E471" s="5" t="n">
-        <v>22.838</v>
-      </c>
-      <c r="F471" s="5" t="n">
-        <v>6.843</v>
-      </c>
-      <c r="G471" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H471" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Basic and diluted (Note 25)</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G471" s="5" t="n">
+        <v>-1.43e-06</v>
+      </c>
+      <c r="H471" s="5" t="n">
+        <v>-8e-08</v>
       </c>
       <c r="I471" t="inlineStr">
         <is>
@@ -53216,30 +53164,30 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>COSTS AND EXPENSES</t>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Interest on convertible loan</t>
+          <t>Equity $660,962 - 14 20 - (780,137) ($119,141)</t>
         </is>
       </c>
       <c r="D472" t="inlineStr"/>
-      <c r="E472" s="5" t="n">
-        <v>7.149</v>
-      </c>
-      <c r="F472" s="5" t="n">
-        <v>13.047</v>
-      </c>
-      <c r="G472" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H472" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G472" s="5" t="n">
+        <v>-162.525</v>
+      </c>
+      <c r="H472" s="5" t="n">
+        <v>-44.313</v>
       </c>
       <c r="I472" t="inlineStr">
         <is>
@@ -53310,34 +53258,30 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>COSTS AND EXPENSES</t>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Foreign exchange (gain) loss</t>
-        </is>
-      </c>
-      <c r="D473" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E473" s="5" t="n">
-        <v>1.636</v>
-      </c>
-      <c r="F473" s="5" t="n">
-        <v>-1.068</v>
-      </c>
-      <c r="G473" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H473" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Deficit ($141,490) - - - - (757,794) ($899,284) - -</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr"/>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G473" s="5" t="n">
+        <v>-943.009</v>
+      </c>
+      <c r="H473" s="5" t="n">
+        <v>-43.725</v>
       </c>
       <c r="I473" t="inlineStr">
         <is>
@@ -53406,22 +53350,22 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B474" t="inlineStr">
-        <is>
-          <t>COSTS AND EXPENSES</t>
-        </is>
-      </c>
+      <c r="B474" t="inlineStr"/>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Impairment of mineral properties (Note 8)</t>
-        </is>
-      </c>
-      <c r="D474" t="inlineStr"/>
+          <t>REVENUES</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E474" s="5" t="n">
-        <v>19.257</v>
+        <v>70.28700000000001</v>
       </c>
       <c r="F474" s="5" t="n">
-        <v>10.954</v>
+        <v>72.373</v>
       </c>
       <c r="G474" t="inlineStr">
         <is>
@@ -53507,17 +53451,19 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>(Gain) on repurchase of convertible loan (Note 11)</t>
-        </is>
-      </c>
-      <c r="D475" t="inlineStr"/>
-      <c r="E475" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Mining operating expenses</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E475" s="5" t="n">
+        <v>63.896</v>
       </c>
       <c r="F475" s="5" t="n">
-        <v>-2.206</v>
+        <v>39.39</v>
       </c>
       <c r="G475" t="inlineStr">
         <is>
@@ -53603,17 +53549,19 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>(Gain) on transfer of mineral properties (Note 8)</t>
-        </is>
-      </c>
-      <c r="D476" t="inlineStr"/>
+          <t>Mining amortization</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E476" s="5" t="n">
-        <v>-1.646</v>
-      </c>
-      <c r="F476" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>17.544</v>
+      </c>
+      <c r="F476" s="5" t="n">
+        <v>10.225</v>
       </c>
       <c r="G476" t="inlineStr">
         <is>
@@ -53699,15 +53647,19 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Litigation and unsuccessful acquisition (Notes 4(b), 14 and 20(b)(ii))</t>
-        </is>
-      </c>
-      <c r="D477" t="inlineStr"/>
+          <t>COSTS AND EXPENSES total</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E477" s="5" t="n">
-        <v>3.348</v>
+        <v>81.44</v>
       </c>
       <c r="F477" s="5" t="n">
-        <v>0.796</v>
+        <v>49.615</v>
       </c>
       <c r="G477" t="inlineStr">
         <is>
@@ -53793,19 +53745,15 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Other expenses</t>
-        </is>
-      </c>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>INCOME (LOSS) FROM MINING OPERATIONS</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr"/>
       <c r="E478" s="5" t="n">
-        <v>0.349</v>
+        <v>-11.153</v>
       </c>
       <c r="F478" s="5" t="n">
-        <v>1.276</v>
+        <v>22.758</v>
       </c>
       <c r="G478" t="inlineStr">
         <is>
@@ -53886,20 +53834,24 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>LOSS BEFORE INCOME TAXES AND NON-CONTROLLING</t>
+          <t>COSTS AND EXPENSES</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>INTEREST</t>
-        </is>
-      </c>
-      <c r="D479" t="inlineStr"/>
+          <t>General and administrative (Note 14)</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E479" s="5" t="n">
-        <v>-83.825</v>
+        <v>19.741</v>
       </c>
       <c r="F479" s="5" t="n">
-        <v>-16.239</v>
+        <v>9.355</v>
       </c>
       <c r="G479" t="inlineStr">
         <is>
@@ -53980,20 +53932,20 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>LOSS BEFORE INCOME TAXES AND NON-CONTROLLING</t>
+          <t>COSTS AND EXPENSES</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Current income taxes expense</t>
+          <t>Stock-based compensation (Note 12(b))</t>
         </is>
       </c>
       <c r="D480" t="inlineStr"/>
       <c r="E480" s="5" t="n">
-        <v>1.611</v>
+        <v>22.838</v>
       </c>
       <c r="F480" s="5" t="n">
-        <v>2.579</v>
+        <v>6.843</v>
       </c>
       <c r="G480" t="inlineStr">
         <is>
@@ -54074,24 +54026,20 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>LOSS BEFORE INCOME TAXES AND NON-CONTROLLING</t>
+          <t>COSTS AND EXPENSES</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Recovery of future income taxes</t>
-        </is>
-      </c>
-      <c r="D481" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Interest on convertible loan</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr"/>
       <c r="E481" s="5" t="n">
-        <v>-13.189</v>
+        <v>7.149</v>
       </c>
       <c r="F481" s="5" t="n">
-        <v>-3.495</v>
+        <v>13.047</v>
       </c>
       <c r="G481" t="inlineStr">
         <is>
@@ -54172,20 +54120,24 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>LOSS BEFORE INCOME TAXES AND NON-CONTROLLING</t>
+          <t>COSTS AND EXPENSES</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>LOSS BEFORE INCOME TAXES AND NON-CONTROLLING total</t>
-        </is>
-      </c>
-      <c r="D482" t="inlineStr"/>
+          <t>Foreign exchange (gain) loss</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E482" s="5" t="n">
-        <v>-11.578</v>
+        <v>1.636</v>
       </c>
       <c r="F482" s="5" t="n">
-        <v>-0.916</v>
+        <v>-1.068</v>
       </c>
       <c r="G482" t="inlineStr">
         <is>
@@ -54266,24 +54218,20 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>LOSS BEFORE INCOME TAXES AND NON-CONTROLLING</t>
+          <t>COSTS AND EXPENSES</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>LOSS BEFORE NON-CONTROLLING INTEREST</t>
-        </is>
-      </c>
-      <c r="D483" t="inlineStr">
-        <is>
-          <t>MinorityInterests</t>
-        </is>
-      </c>
+          <t>Impairment of mineral properties (Note 8)</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr"/>
       <c r="E483" s="5" t="n">
-        <v>72.247</v>
+        <v>19.257</v>
       </c>
       <c r="F483" s="5" t="n">
-        <v>15.323</v>
+        <v>10.954</v>
       </c>
       <c r="G483" t="inlineStr">
         <is>
@@ -54364,26 +54312,22 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>LOSS BEFORE INCOME TAXES AND NON-CONTROLLING</t>
+          <t>COSTS AND EXPENSES</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Non-controlling interest</t>
-        </is>
-      </c>
-      <c r="D484" t="inlineStr">
-        <is>
-          <t>MinorityInterests</t>
-        </is>
-      </c>
+          <t>(Gain) on repurchase of convertible loan (Note 11)</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr"/>
       <c r="E484" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F484" s="5" t="n">
-        <v>0.961</v>
+        <v>-2.206</v>
       </c>
       <c r="G484" t="inlineStr">
         <is>
@@ -54464,24 +54408,22 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>LOSS BEFORE INCOME TAXES AND NON-CONTROLLING</t>
+          <t>COSTS AND EXPENSES</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>NET LOSS</t>
-        </is>
-      </c>
-      <c r="D485" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>(Gain) on transfer of mineral properties (Note 8)</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr"/>
       <c r="E485" s="5" t="n">
-        <v>-72.247</v>
-      </c>
-      <c r="F485" s="5" t="n">
-        <v>-16.284</v>
+        <v>-1.646</v>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G485" t="inlineStr">
         <is>
@@ -54562,20 +54504,20 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>LOSS BEFORE INCOME TAXES AND NON-CONTROLLING</t>
+          <t>COSTS AND EXPENSES</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Deficit, beginning of year</t>
+          <t>Litigation and unsuccessful acquisition (Notes 4(b), 14 and 20(b)(ii))</t>
         </is>
       </c>
       <c r="D486" t="inlineStr"/>
       <c r="E486" s="5" t="n">
-        <v>-95.28400000000001</v>
+        <v>3.348</v>
       </c>
       <c r="F486" s="5" t="n">
-        <v>-167.531</v>
+        <v>0.796</v>
       </c>
       <c r="G486" t="inlineStr">
         <is>
@@ -54656,22 +54598,24 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>LOSS BEFORE INCOME TAXES AND NON-CONTROLLING</t>
+          <t>COSTS AND EXPENSES</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Repurchase of convertible loan (Note 11)</t>
-        </is>
-      </c>
-      <c r="D487" t="inlineStr"/>
-      <c r="E487" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E487" s="5" t="n">
+        <v>0.349</v>
       </c>
       <c r="F487" s="5" t="n">
-        <v>1.577</v>
+        <v>1.276</v>
       </c>
       <c r="G487" t="inlineStr">
         <is>
@@ -54757,15 +54701,15 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>DEFICIT, END OF YEAR</t>
+          <t>INTEREST</t>
         </is>
       </c>
       <c r="D488" t="inlineStr"/>
       <c r="E488" s="5" t="n">
-        <v>-167.531</v>
+        <v>-83.825</v>
       </c>
       <c r="F488" s="5" t="n">
-        <v>-182.238</v>
+        <v>-16.239</v>
       </c>
       <c r="G488" t="inlineStr">
         <is>
@@ -54851,19 +54795,15 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
-        </is>
-      </c>
-      <c r="D489" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>Current income taxes expense</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr"/>
       <c r="E489" s="5" t="n">
-        <v>0.389132</v>
+        <v>1.611</v>
       </c>
       <c r="F489" s="5" t="n">
-        <v>0.501074</v>
+        <v>2.579</v>
       </c>
       <c r="G489" t="inlineStr">
         <is>
@@ -54949,86 +54889,956 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
+          <t>Recovery of future income taxes</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E490" s="5" t="n">
+        <v>-13.189</v>
+      </c>
+      <c r="F490" s="5" t="n">
+        <v>-3.495</v>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>LOSS BEFORE INCOME TAXES AND NON-CONTROLLING</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>LOSS BEFORE INCOME TAXES AND NON-CONTROLLING total</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr"/>
+      <c r="E491" s="5" t="n">
+        <v>-11.578</v>
+      </c>
+      <c r="F491" s="5" t="n">
+        <v>-0.916</v>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>LOSS BEFORE INCOME TAXES AND NON-CONTROLLING</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>LOSS BEFORE NON-CONTROLLING INTEREST</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
+      <c r="E492" s="5" t="n">
+        <v>72.247</v>
+      </c>
+      <c r="F492" s="5" t="n">
+        <v>15.323</v>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>LOSS BEFORE INCOME TAXES AND NON-CONTROLLING</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Non-controlling interest</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F493" s="5" t="n">
+        <v>0.961</v>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>LOSS BEFORE INCOME TAXES AND NON-CONTROLLING</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>NET LOSS</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E494" s="5" t="n">
+        <v>-72.247</v>
+      </c>
+      <c r="F494" s="5" t="n">
+        <v>-16.284</v>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>LOSS BEFORE INCOME TAXES AND NON-CONTROLLING</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Deficit, beginning of year</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr"/>
+      <c r="E495" s="5" t="n">
+        <v>-95.28400000000001</v>
+      </c>
+      <c r="F495" s="5" t="n">
+        <v>-167.531</v>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>LOSS BEFORE INCOME TAXES AND NON-CONTROLLING</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Repurchase of convertible loan (Note 11)</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr"/>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F496" s="5" t="n">
+        <v>1.577</v>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>LOSS BEFORE INCOME TAXES AND NON-CONTROLLING</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>DEFICIT, END OF YEAR</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr"/>
+      <c r="E497" s="5" t="n">
+        <v>-167.531</v>
+      </c>
+      <c r="F497" s="5" t="n">
+        <v>-182.238</v>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>LOSS BEFORE INCOME TAXES AND NON-CONTROLLING</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E498" s="5" t="n">
+        <v>0.389132</v>
+      </c>
+      <c r="F498" s="5" t="n">
+        <v>0.501074</v>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>LOSS BEFORE INCOME TAXES AND NON-CONTROLLING</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
           <t>BASIC AND DILUTED LOSS PER SHARE</t>
         </is>
       </c>
-      <c r="D490" t="inlineStr">
+      <c r="D499" t="inlineStr">
         <is>
           <t>BasicEPS</t>
         </is>
       </c>
-      <c r="E490" s="5" t="n">
+      <c r="E499" s="5" t="n">
         <v>-1.9e-07</v>
       </c>
-      <c r="F490" s="5" t="n">
+      <c r="F499" s="5" t="n">
         <v>-3e-08</v>
       </c>
-      <c r="G490" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H490" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I490" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J490" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K490" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L490" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M490" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N490" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O490" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P490" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q490" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R490" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S490" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T490" t="inlineStr">
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T499" t="inlineStr">
         <is>
           <t>-</t>
         </is>
